--- a/prep_and_checklists/Cara Brophy  /PREP_REQ_Cara Brophy  _Saturday, March 21, 2026  _0.xlsx
+++ b/prep_and_checklists/Cara Brophy  /PREP_REQ_Cara Brophy  _Saturday, March 21, 2026  _0.xlsx
@@ -8,14 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidcuvin/purveyor_project/prep_and_checklists/Cara Brophy  /"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E93305BA-3E67-154C-8012-F0B530DC6EA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B05B6999-C35A-284E-B781-63C6302DA95C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2960" windowWidth="29940" windowHeight="17600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="880" windowWidth="29940" windowHeight="17600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Prep Req" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -49,9 +62,6 @@
     <t xml:space="preserve">Saturday, March 21, 2026  , before 8:00 PM </t>
   </si>
   <si>
-    <t>re-form 2oz sliders</t>
-  </si>
-  <si>
     <t>smoked onion aioli</t>
   </si>
   <si>
@@ -101,6 +111,9 @@
   </si>
   <si>
     <t>2 pints</t>
+  </si>
+  <si>
+    <t>re-form 2oz sliders, 3in Diameter</t>
   </si>
 </sst>
 </file>
@@ -586,10 +599,10 @@
     </row>
     <row r="3" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="12" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C3" s="12" t="s">
         <v>7</v>
@@ -618,10 +631,10 @@
     </row>
     <row r="4" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>7</v>
@@ -650,10 +663,10 @@
     </row>
     <row r="5" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>7</v>
@@ -682,10 +695,10 @@
     </row>
     <row r="6" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>7</v>
@@ -714,10 +727,10 @@
     </row>
     <row r="7" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>7</v>
@@ -746,10 +759,10 @@
     </row>
     <row r="8" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>7</v>
@@ -778,10 +791,10 @@
     </row>
     <row r="9" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>7</v>
@@ -810,10 +823,10 @@
     </row>
     <row r="10" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C10" s="12" t="s">
         <v>7</v>
@@ -842,10 +855,10 @@
     </row>
     <row r="11" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>7</v>
@@ -874,10 +887,10 @@
     </row>
     <row r="12" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>7</v>
@@ -906,10 +919,10 @@
     </row>
     <row r="13" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C13" s="12" t="s">
         <v>7</v>
@@ -938,7 +951,7 @@
     </row>
     <row r="14" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" s="12"/>
       <c r="C14" s="12" t="s">
